--- a/IgniteDigitalization.Server/Initializers/IGNITE_S2_Innowacja.xlsx
+++ b/IgniteDigitalization.Server/Initializers/IGNITE_S2_Innowacja.xlsx
@@ -7,12 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feedbacks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardsWeights" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardsEnablers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boards" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feedbacks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardsWeights" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardsEnablers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EconomyRules" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -375,6 +377,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Labels_Up</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Labels_Right</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Description_Down</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Description_Left</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Cols</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Border_Color</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Cell_Color</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Borders_Colors</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Cells_Descriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Weryfikacja Rynkowa Innowacji</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Etap komercjalizacji;Trafność przekazu innowacji;Penetracja segmentu;Klarowność kierunku innowacji;</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Rentowność innowacji;Rozpoznawalność innowacji;Lojalność pierwszych klientów;Morale i zaangażowanie;</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>#595959</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>#212121</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>#5faf4c;#f9e44d;#00b8e4;#e32e81</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Zysk;Widoczność;Udział w rynku;Motywacja Zespołu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Analiza Hipotez</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Podstawowa;Zintegrowana;Inteligentna;Autonomiczna</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Operacyjna;Adaptacyjna;Strategiczna;Innowacyjna</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Automatyzacja Procesów</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Zwinność Procesów</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>#212121</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#fefae0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>#008000;#FFFF00;#FFA500;#FF0000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -444,7 +608,7 @@
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
-          <t>Card_Phase</t>
+          <t>Card_Phase_Dup</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1945,7 +2109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2124,7 +2288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2307,7 +2471,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2370,10 +2534,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -2400,10 +2564,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>1</v>
@@ -2430,10 +2594,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>1</v>
@@ -2460,10 +2624,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>1</v>
@@ -2490,10 +2654,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>1</v>
@@ -2520,10 +2684,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>1</v>
@@ -2550,10 +2714,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1</v>
@@ -2580,10 +2744,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
@@ -2610,10 +2774,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1</v>
@@ -2640,10 +2804,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
@@ -2670,10 +2834,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>1</v>
@@ -2700,10 +2864,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
@@ -2730,10 +2894,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1</v>
@@ -2760,10 +2924,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
@@ -2790,10 +2954,10 @@
         <v>3</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1</v>
@@ -2820,10 +2984,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>1</v>
@@ -2850,10 +3014,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>1</v>
@@ -2880,10 +3044,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>1</v>
@@ -2910,10 +3074,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1</v>
@@ -2940,10 +3104,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>1</v>
@@ -2970,10 +3134,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>1</v>
@@ -3000,10 +3164,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>1</v>
@@ -3030,10 +3194,10 @@
         <v>3</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1</v>
@@ -3060,10 +3224,10 @@
         <v>4</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>1</v>
@@ -3090,10 +3254,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1</v>
@@ -3120,10 +3284,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>1</v>
@@ -3150,10 +3314,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1</v>
@@ -3180,10 +3344,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1</v>
@@ -3210,10 +3374,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
@@ -3240,10 +3404,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>1</v>
@@ -3270,10 +3434,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1</v>
@@ -3300,10 +3464,10 @@
         <v>4</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>1</v>
@@ -3330,10 +3494,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1</v>
@@ -3360,10 +3524,10 @@
         <v>2</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>1</v>
@@ -3390,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1</v>
@@ -3420,10 +3584,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>1</v>
@@ -3450,10 +3614,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1</v>
@@ -3480,10 +3644,10 @@
         <v>2</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>1</v>
@@ -3510,10 +3674,10 @@
         <v>3</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
@@ -3540,10 +3704,10 @@
         <v>4</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>1</v>
@@ -6209,7 +6373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6247,10 +6411,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>11</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -6258,17 +6422,17 @@
           <t>Crowdfunding wymaga strony docelowej, na którą kierujesz ruch — bez landing page nie masz dokąd odsyłać potencjalnych backerów.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>PODWÓJNY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>14</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -6276,17 +6440,17 @@
           <t>Kampania pre-sprzedażowa bez zbudowanej społeczności w social media to krzyczeniew próżnię — nie masz zasięgu ani zaangażowania które napędzą zbiórkę.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>PODWÓJNY</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>17</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -6294,17 +6458,17 @@
           <t>Nie możesz testować użyteczności czegoś co nie działa — testy użytkowników wymagają działającego prototypu, nie renderingu ani makiety.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>POJEDYNCZY</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>18</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -6312,17 +6476,17 @@
           <t>Iteracja produktu musi być oparta na danych z testów użytkowników — bez nich zmieniasz produkt na ślepo, nie wiedząc co naprawdę nie działa.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>POJEDYNCZY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>17</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -6330,17 +6494,17 @@
           <t>Pilotaż to oddanie prawdziwego urządzenia w ręce klientów — bez działającego prototypu nie masz czego testować w warunkach rzeczywistych.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>PODWÓJNY</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>18</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6348,17 +6512,17 @@
           <t>Wysyłanie produktu na pilotaż bez wcześniejszych testów użyteczności to ryzykowanie, że pierwsi klienci dostaną wadliwy sprzęt i staną się krytykami zamiast ambasadorami.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>PODWÓJNY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6366,17 +6530,17 @@
           <t>Ekspansja na nowy segment bez udanego pilotażu w pierwszym to skalowanie nieznanego — nie wiesz co działało i dlaczego, więc nie masz czego replikować.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>POJEDYNCZY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>26</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -6384,17 +6548,17 @@
           <t>Model finansowy skalowania bez planu komercjalizacji to kalkulacja w próżni — nie znasz harmonogramu przychodów, kosztów per etap ani momentów zapotrzebowania na kapitał.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>POJEDYNCZY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>22</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -6402,9 +6566,357 @@
           <t>Eco-storytelling bez certyfikacji ekologicznej to greenwashing — w erze Green Claims Directive EU każde twierdzenie o ekologii musi być udokumentowane, a nie tylko ładnie brzmięć.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>POJEDYNCZY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" style="4" min="1" max="1"/>
+    <col width="40" customWidth="1" style="4" min="2" max="2"/>
+    <col width="70" customWidth="1" style="4" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>📊  EKONOMIA GRY — IGNITE S2: Innowacja</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Waluta: BITY  |  Zasada ogólna: Zasoby są ograniczone — gracz musi strategicznie wybierać karty i alokować zasoby między hipotezy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MAPA 1 — Budżet startowy (Faza Analizy Hipotez)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Budżet startowy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24 bity</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wystarczy na 8–9 z 10 dostępnych kart (koszt karty = 2 bity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Karty obowiązkowe</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mapa 1 nie ma enablerów — gracz ma pełną swobodę wyboru</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cel projektowy Mapa 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7–9 kart zagranych</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Gracz nie może zagrać wszystkich — musi priorytetyzować obszary analizy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MAPA 2 — Budżet rynkowy (dynamiczny)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Budżet bazowy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>32 bity</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Każdy zespół startuje na Mapie 2 z tym samym bazowym budżetem</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bonus przygotowania</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(kart_PRE / 10) × 12 bitów</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Maksymalny bonus: +12 bitów (jeśli zagrano wszystkie 10 kart PRE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Formuła aplikacji</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>MIN(44 ; 32 + ROUND((pre/10)*12, 0))</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aplikacja wylicza budżet Map 2 automatycznie po zakończeniu Map 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Zakres budżetu Mapa 2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>34–44 bity</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Min: 3 karty PRE → ~36 bitów | Max: 10 kart PRE → 44 bity</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cel projektowy Mapa 2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11–15 kart zagranych</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gracz musi wybrać strategię: widoczność vs zysk vs rynek vs motywacja</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MNOŻNIK PRZYGOTOWANIA — wpływ Mapy 1 na efekty Mapy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Formuła</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mnożnik_Wagi = MIN(2,0 ; 1 + kart_PRE_zagranych / 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3 kart PRE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>×1,30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>minimum — efekty rynkowe o 30% silniejsze niż bazowe</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5 kart PRE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>×1,50</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>średnie przygotowanie</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8 kart PRE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>×1,80</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dobre przygotowanie</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>10 kart PRE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>×2,00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>maximum — każda karta rynkowa działa 2× silniej</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MECHANIKA HIPOTEZ INNOWACYJNYCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pula hipotez startowa</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10 hipotez do wyboru</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Grill na podczerwieni, grill na wodór, grill solarny, grill pelletowy smart, grill modularny, grill dla kampera, grill profesjonalny HoReCa, grill zero-waste, grill na bioetanol, grill hybrydowy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Analiza na Mapie 1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dowolne spośród 10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Na Mapie 1 można analizować wszystkie — karty pogłębiają analizę każdej hipotezy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wybór do Mapy 2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2 hipotezy</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Gracze wybierają 2 hipotezy do weryfikacji rynkowej na Mapie 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Rozgrywka per hipoteza</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mapa 2 działa per hipotezę</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Zasoby Mapy 2 alokowane między 2 hipotezy — koncentracja vs dywersyfikacja to kluczowy wybór</t>
         </is>
       </c>
     </row>

--- a/IgniteDigitalization.Server/Initializers/IGNITE_S2_Innowacja.xlsx
+++ b/IgniteDigitalization.Server/Initializers/IGNITE_S2_Innowacja.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc" lowestEdited="7"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Boards" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="248">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -194,14 +194,13 @@
     <t xml:space="preserve">Pomysł na papierze to jeszcze nie produkt. Budujesz pierwszy namacalny artefakt — render 3D, makietę, model kartonowy, animację działania — i kładziesz to przed potencjalnymi klientami. Obserwujesz ich twarze zanim powiesz cokolwiek. Czy biorą to do rąk z ciekawością czy z dystansem? Pięć szczerych reakcji na coś co można dotknąć jest warte więcej niż trzy miesiące analizy przy biurku.</t>
   </si>
   <si>
-    <t xml:space="preserve">★ WEJŚCIE NA RYNEK INNOWACJI ★</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To jest moment. Oficjalnie uruchamiasz swój innowacyjny produkt i wchodzisz na rynek. Od tej chwili zaczyna się Mapa 2 — walka o klientów, widoczność i zysk. Im lepiej przygotowałeś się na Mapie 1, tym silniejsze będą efekty każdej kolejnej decyzji.
-Nie wymaga żadnych innych kart — wystarczy odwaga i gotowość do konfrontacji z rynkiem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WEJŚCIE NA RYNEK ★</t>
+    <t xml:space="preserve">Sformułowanie hipotez biznesowych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czas zamienić luźne pomysły w konkretne, mierzalne założenia. Formułujesz dziesięć hipotez produktowych — każda opisuje jaki produkt, dla kogo, w jakiej cenie i dlaczego miałby zadziałać na rynku. Następnie każdą hipotezę rozkładasz na planszy według dwóch wymiarów: jak duże ma znaczenie dla powodzenia całego przedsięwzięcia oraz jaki jest jej stopień udokumentowania.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★ WEJŚCIE NA RYNEK ★</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page MVP</t>
@@ -402,6 +401,9 @@
     <t xml:space="preserve">Prototyp koncepcji gotowy i pokazany klientom. Ich pierwsza reakcja jest bezcennym sygnałem rynkowym.</t>
   </si>
   <si>
+    <t xml:space="preserve">Dziesięć hipotez produktowych sformułowanych i rozłożonych na mapie. Masz konkretne, mierzalne założenia.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Landing page działa i zbiera konwersje. Masz twarde dane o zainteresowaniu rynku zanim produkt istnieje. Badaj rynek zanim wyprodukujesz — zostawiony kontakt to dowód że warto inwestować. Słabe wyniki to często wina reklamy, nie produktu. Po 72 godzinach od kontaktu 80% ludzi traci zainteresowanie — pierwsza wiadomość powinna dotrzeć w ciągu godziny.</t>
   </si>
   <si>
@@ -492,12 +494,6 @@
     <t xml:space="preserve">Weryfikacja zakończona. Zestawiono plan z rzeczywistością — zespół podjął świadomą decyzję: skalować, korygować, czy wycofać się z godnością.</t>
   </si>
   <si>
-    <t xml:space="preserve">Oficjalny start! Mapa 2 jest odblokowana. Mnożnik przygotowania aktywny — Twoje decyzje rynkowe są tym silniejsze im więcej kart zagrałeś na Mapie 1. Czas na zdobywanie rynku.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Próbujesz wejść na rynek bez jakiegokolwiek przygotowania. Innowacja bez zwalidowanych hipotez, bez zrozumienia klienta i bez modelu finansowego to zakład który rzadko wygrywa. Rynek nie wybacza naiwności.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Processes_Id</t>
   </si>
   <si>
@@ -570,9 +566,6 @@
     <t xml:space="preserve">PRZYGOTOWAWCZA</t>
   </si>
   <si>
-    <t xml:space="preserve">WEJŚCIE NA RYNEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">RYNKOWA</t>
   </si>
   <si>
@@ -627,7 +620,7 @@
     <t xml:space="preserve">Budżet startowy</t>
   </si>
   <si>
-    <t xml:space="preserve">24 bity</t>
+    <t xml:space="preserve">14 bity</t>
   </si>
   <si>
     <t xml:space="preserve">Wystarczy na 8–9 z 10 dostępnych kart (koszt karty = 2 bity)</t>
@@ -1150,7 +1143,7 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1991,7 +1984,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -2111,7 +2104,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>114</v>
@@ -2122,7 +2115,7 @@
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>114</v>
@@ -2136,18 +2129,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>128</v>
@@ -2155,7 +2148,7 @@
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>114</v>
@@ -2166,7 +2159,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>114</v>
@@ -2177,7 +2170,7 @@
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>114</v>
@@ -2188,7 +2181,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>114</v>
@@ -2202,7 +2195,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>133</v>
@@ -2210,10 +2203,10 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>134</v>
@@ -2224,7 +2217,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>135</v>
@@ -2232,10 +2225,10 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>136</v>
@@ -2243,7 +2236,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>114</v>
@@ -2257,7 +2250,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>138</v>
@@ -2265,10 +2258,10 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>139</v>
@@ -2276,7 +2269,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>114</v>
@@ -2287,7 +2280,7 @@
     </row>
     <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>114</v>
@@ -2298,7 +2291,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>114</v>
@@ -2309,7 +2302,7 @@
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>114</v>
@@ -2323,7 +2316,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>144</v>
@@ -2331,10 +2324,10 @@
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>145</v>
@@ -2342,7 +2335,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>114</v>
@@ -2353,7 +2346,7 @@
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>114</v>
@@ -2367,7 +2360,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>148</v>
@@ -2375,10 +2368,10 @@
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>149</v>
@@ -2386,7 +2379,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>114</v>
@@ -2400,7 +2393,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>151</v>
@@ -2408,10 +2401,10 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>152</v>
@@ -2419,7 +2412,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>114</v>
@@ -2430,24 +2423,13 @@
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="3" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2471,22 +2453,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>32</v>
@@ -2503,13 +2485,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="D2" s="0" t="s">
         <v>163</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>164</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>0.25</v>
@@ -2526,13 +2508,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="D3" s="0" t="s">
         <v>166</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>167</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>0.25</v>
@@ -2549,13 +2531,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="D4" s="0" t="s">
         <v>169</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>170</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>0.25</v>
@@ -2572,13 +2554,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="D5" s="0" t="s">
         <v>172</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>173</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>0.25</v>
@@ -2802,25 +2784,25 @@
         <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2843,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2869,10 +2851,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2895,10 +2877,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2921,10 +2903,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2947,10 +2929,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2973,10 +2955,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2999,10 +2981,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3025,10 +3007,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3051,10 +3033,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3077,10 +3059,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3103,10 +3085,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3129,10 +3111,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3155,10 +3137,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3181,10 +3163,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3207,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3233,10 +3215,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3259,10 +3241,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3285,10 +3267,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3311,10 +3293,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3337,10 +3319,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3363,10 +3345,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3389,10 +3371,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3415,10 +3397,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3441,10 +3423,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3467,10 +3449,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3493,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3519,10 +3501,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3545,10 +3527,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3571,10 +3553,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3597,10 +3579,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3623,10 +3605,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3649,10 +3631,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3675,10 +3657,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3701,10 +3683,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3727,10 +3709,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3753,10 +3735,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3767,10 +3749,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="0" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>1</v>
@@ -3779,10 +3761,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3793,10 +3775,10 @@
         <v>2</v>
       </c>
       <c r="C39" s="0" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E39" s="0" t="n">
         <v>1</v>
@@ -3805,10 +3787,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3819,10 +3801,10 @@
         <v>3</v>
       </c>
       <c r="C40" s="0" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E40" s="0" t="n">
         <v>1</v>
@@ -3831,10 +3813,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3845,10 +3827,10 @@
         <v>4</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>1</v>
@@ -3857,10 +3839,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3883,10 +3865,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3909,10 +3891,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3935,10 +3917,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3961,10 +3943,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3987,10 +3969,10 @@
         <v>1</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4013,10 +3995,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4039,10 +4021,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4065,10 +4047,10 @@
         <v>1</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4091,10 +4073,10 @@
         <v>1</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4117,10 +4099,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4143,10 +4125,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4169,10 +4151,10 @@
         <v>1</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4195,10 +4177,10 @@
         <v>1</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4221,10 +4203,10 @@
         <v>1</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4247,10 +4229,10 @@
         <v>1</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4273,10 +4255,10 @@
         <v>1</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4299,10 +4281,10 @@
         <v>1</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4325,10 +4307,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4351,10 +4333,10 @@
         <v>1</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4377,10 +4359,10 @@
         <v>1</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4403,10 +4385,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4429,10 +4411,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4455,10 +4437,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4481,10 +4463,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4507,10 +4489,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4533,10 +4515,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4559,10 +4541,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4585,10 +4567,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4611,10 +4593,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4637,10 +4619,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4663,10 +4645,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4689,10 +4671,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4715,10 +4697,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4741,10 +4723,10 @@
         <v>1</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4767,10 +4749,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4793,10 +4775,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4819,10 +4801,10 @@
         <v>1</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4845,10 +4827,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4871,10 +4853,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4897,10 +4879,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4923,10 +4905,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4949,10 +4931,10 @@
         <v>1</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4975,10 +4957,10 @@
         <v>1</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5001,10 +4983,10 @@
         <v>1</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5027,10 +5009,10 @@
         <v>1</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5053,10 +5035,10 @@
         <v>1</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5079,10 +5061,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5105,10 +5087,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5131,10 +5113,10 @@
         <v>1</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5157,10 +5139,10 @@
         <v>1</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5183,10 +5165,10 @@
         <v>1</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5209,10 +5191,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5235,10 +5217,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5261,10 +5243,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5287,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5313,10 +5295,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5339,10 +5321,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5365,10 +5347,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5391,10 +5373,10 @@
         <v>1</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5417,10 +5399,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5443,10 +5425,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5469,10 +5451,10 @@
         <v>1</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5495,10 +5477,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5521,10 +5503,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5547,10 +5529,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5573,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5599,10 +5581,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5625,10 +5607,10 @@
         <v>1</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5651,10 +5633,10 @@
         <v>1</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5677,10 +5659,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5703,10 +5685,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5729,10 +5711,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5755,10 +5737,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5781,10 +5763,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5807,10 +5789,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5833,10 +5815,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5859,10 +5841,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5885,10 +5867,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5911,10 +5893,10 @@
         <v>1</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5937,10 +5919,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5963,10 +5945,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5989,10 +5971,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6015,10 +5997,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6041,10 +6023,10 @@
         <v>1</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6070,7 +6052,7 @@
         <v>110</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6096,7 +6078,7 @@
         <v>110</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6122,7 +6104,7 @@
         <v>110</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6148,7 +6130,7 @@
         <v>110</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -6176,7 +6158,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -6184,13 +6166,13 @@
         <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>12</v>
       </c>
@@ -6198,13 +6180,13 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
         <v>12</v>
       </c>
@@ -6212,13 +6194,13 @@
         <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
         <v>18</v>
       </c>
@@ -6226,13 +6208,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
         <v>19</v>
       </c>
@@ -6240,13 +6222,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
         <v>20</v>
       </c>
@@ -6254,13 +6236,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
         <v>20</v>
       </c>
@@ -6268,13 +6250,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
         <v>25</v>
       </c>
@@ -6282,13 +6264,13 @@
         <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
         <v>28</v>
       </c>
@@ -6296,13 +6278,13 @@
         <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
         <v>30</v>
       </c>
@@ -6310,10 +6292,10 @@
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -6342,213 +6324,213 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="0" t="s">
         <v>198</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="0" t="s">
         <v>201</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>204</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" s="0" t="s">
         <v>208</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="C11" s="0" t="s">
         <v>211</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="0" t="s">
         <v>216</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="0" t="s">
         <v>219</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" s="0" t="s">
         <v>225</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="0" t="s">
         <v>228</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>229</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="0" t="s">
         <v>231</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="0" t="s">
         <v>234</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="C24" s="0" t="s">
         <v>238</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>239</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="0" t="s">
         <v>241</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="0" t="s">
         <v>244</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="0" t="s">
         <v>247</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>
